--- a/data/trans_orig/IP3111_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>23549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>25267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40600</t>
+          <t>39967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24717</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35095</t>
+          <t>36210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25956</t>
+          <t>26522</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>43884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49796</t>
+          <t>50368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74024</t>
+          <t>73770</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>30573</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31884</t>
+          <t>32012</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51082</t>
+          <t>52213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52290</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77518</t>
+          <t>75948</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>27905</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>43540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>33259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>53833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65492</t>
+          <t>64775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91582</t>
+          <t>91869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>25025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42233</t>
+          <t>42306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30528</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>43893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67342</t>
+          <t>68022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>22507</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16682</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31821</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>51310</t>
+          <t>51818</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>34974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11489</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24889</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34326</t>
+          <t>33912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55487</t>
+          <t>54858</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>15855</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>31606</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34588</t>
+          <t>35094</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59922</t>
+          <t>60954</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28166</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48487</t>
+          <t>48314</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34105</t>
+          <t>34980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57412</t>
+          <t>59316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66909</t>
+          <t>67416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99117</t>
+          <t>100882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>25959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45524</t>
+          <t>45245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40440</t>
+          <t>41448</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63083</t>
+          <t>63221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71988</t>
+          <t>71829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101059</t>
+          <t>101212</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26682</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>47768</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47605</t>
+          <t>47606</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59003</t>
+          <t>58267</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>89678</t>
+          <t>87075</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33802</t>
+          <t>34144</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>40164</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41258</t>
+          <t>41686</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65750</t>
+          <t>65778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>26361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38978</t>
+          <t>37986</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>34800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58371</t>
+          <t>58968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35901</t>
+          <t>36186</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>28900</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51567</t>
+          <t>52996</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29064</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55054</t>
+          <t>56893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49992</t>
+          <t>49397</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>81394</t>
+          <t>82538</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>85081</t>
+          <t>87652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>130570</t>
+          <t>129311</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43289</t>
+          <t>44615</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>80662</t>
+          <t>80490</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>80203</t>
+          <t>79303</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>104487</t>
+          <t>106602</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>151811</t>
+          <t>151903</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32210</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58557</t>
+          <t>58182</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>48054</t>
+          <t>47766</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76771</t>
+          <t>76942</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87528</t>
+          <t>86292</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>126552</t>
+          <t>127241</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>37834</t>
+          <t>36855</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>123620</t>
+          <t>130995</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27189</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55414</t>
+          <t>54296</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>73152</t>
+          <t>72853</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>189015</t>
+          <t>174061</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40886</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38898</t>
+          <t>40012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90071</t>
+          <t>90012</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>65930</t>
+          <t>67277</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>122323</t>
+          <t>125869</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>77515</t>
+          <t>75474</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>110500</t>
+          <t>109000</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>72019</t>
+          <t>71916</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>103203</t>
+          <t>105058</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>156436</t>
+          <t>156966</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>202343</t>
+          <t>203756</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>91458</t>
+          <t>90944</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>129554</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>141526</t>
+          <t>140045</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>186054</t>
+          <t>186041</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>243091</t>
+          <t>241040</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>305736</t>
+          <t>301823</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>119349</t>
+          <t>117069</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>162772</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>146851</t>
+          <t>146559</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>189445</t>
+          <t>188540</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>277598</t>
+          <t>272879</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>336200</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>100901</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>139265</t>
+          <t>141985</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>106512</t>
+          <t>107541</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>146789</t>
+          <t>145141</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>213906</t>
+          <t>216611</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>271758</t>
+          <t>271559</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>80089</t>
+          <t>79793</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>191499</t>
+          <t>192722</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>77547</t>
+          <t>76601</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>118360</t>
+          <t>116508</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>169208</t>
+          <t>172030</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>286309</t>
+          <t>280696</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>64296</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>96969</t>
+          <t>96381</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>82406</t>
+          <t>83954</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>141050</t>
+          <t>144583</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>156569</t>
+          <t>154387</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>224265</t>
+          <t>217996</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3111_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10902</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7425</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14753</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18196</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13113</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23549</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>20891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32537</t>
+          <t>27081</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39967</t>
+          <t>33083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6477</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13983</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6957</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3866</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11755</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13257</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3668</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10239</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,67%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>27,35%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6695</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3710</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10991</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21943</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4054</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7480</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6016</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3019</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10072</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3718</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7180</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4725</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8876</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5659</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3906</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1614</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>7476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>16,08%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42681</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>45285</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>164</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29494</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22967</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38660</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>26766</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19952</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36210</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>26023</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26522</t>
+          <t>19331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>61499</t>
+          <t>55517</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50368</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73770</t>
+          <t>66460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35241</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27499</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43942</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>22,44%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>17,51%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>27,98%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>23046</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16537</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30573</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,19%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41335</t>
+          <t>20859</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32012</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>64381</t>
+          <t>56100</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>75948</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36423</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28157</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46059</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>35398</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27905</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>43540</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42454</t>
+          <t>34038</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33259</t>
+          <t>26476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53833</t>
+          <t>42968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>77852</t>
+          <t>70461</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64775</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91869</t>
+          <t>83030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19217</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13275</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27595</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>32393</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25025</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42306</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>27577</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15247</t>
+          <t>20848</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>54193</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43893</t>
+          <t>37069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68022</t>
+          <t>56602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>21349</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15075</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>27653</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>17,61%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>15774</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>10625</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>22507</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>15029</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16310</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>40057</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>51818</t>
+          <t>45559</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15317</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10607</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22221</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>25923</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18569</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34974</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25312</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43276</t>
+          <t>37310</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54858</t>
+          <t>46543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>181959</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>181959</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>181959</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>533</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22511</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14885</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32515</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>22694</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>15855</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>31606</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,26%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35094</t>
+          <t>31699</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>46679</t>
+          <t>46551</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60954</t>
+          <t>59650</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>41065</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>31091</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>51197</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>25,58%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>37403</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>28409</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>48314</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>21,61%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>27,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45452</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34980</t>
+          <t>27156</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59316</t>
+          <t>46036</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>82855</t>
+          <t>77486</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67416</t>
+          <t>63600</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100882</t>
+          <t>92228</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48367</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>38488</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>59569</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>24,17%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>29,77%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>34664</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>25959</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>45245</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>51171</t>
+          <t>36142</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41448</t>
+          <t>27093</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63221</t>
+          <t>45937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>85835</t>
+          <t>84509</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71829</t>
+          <t>70030</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101212</t>
+          <t>99777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>34412</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26682</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47768</t>
+          <t>44916</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27300</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47606</t>
+          <t>43573</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>58267</t>
+          <t>55585</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>87075</t>
+          <t>83390</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26482</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19088</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>36734</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>25089</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>17702</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>34144</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27498</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40164</t>
+          <t>34449</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>52587</t>
+          <t>52664</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41686</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65778</t>
+          <t>65523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>27289</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>19502</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>39320</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>18024</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>11033</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>26361</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>12185</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>25953</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>27896</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>19459</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>37986</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>45921</t>
+          <t>45470</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>34302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58968</t>
+          <t>58021</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>476</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>14511</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>8575</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>22917</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>25206</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>16855</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>36186</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>37108</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>41217</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28900</t>
+          <t>30965</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52996</t>
+          <t>54080</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>61869</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>47048</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>78269</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>21,47%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>27,17%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>43339</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>29898</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>56893</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>20,98%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>64394</t>
+          <t>43278</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49397</t>
+          <t>33184</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82538</t>
+          <t>54308</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>105147</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87652</t>
+          <t>88301</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>129311</t>
+          <t>123705</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>63213</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>50602</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>77382</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>21,94%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>63001</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>44615</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>80490</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>16,45%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65062</t>
+          <t>61231</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>50335</t>
+          <t>50536</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>79303</t>
+          <t>75558</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>128063</t>
+          <t>124444</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>106602</t>
+          <t>106350</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>151903</t>
+          <t>143622</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>61125</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>48225</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>76231</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>16,74%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>26,46%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>45595</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>32177</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>58182</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>62192</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47766</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76942</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>107787</t>
+          <t>108509</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86292</t>
+          <t>91724</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>127241</t>
+          <t>126311</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>37040</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>26433</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>52572</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>18,25%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>63337</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>36855</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>130995</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>23,35%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>48,3%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27827</t>
+          <t>29903</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54296</t>
+          <t>52271</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>101744</t>
+          <t>77151</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>72853</t>
+          <t>62827</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>174061</t>
+          <t>94138</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>50346</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>35853</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>72316</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>17,48%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>25,1%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>30747</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>19805</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>41427</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>56964</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40012</t>
+          <t>24885</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90012</t>
+          <t>43959</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>87712</t>
+          <t>84001</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>67277</t>
+          <t>65052</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>125869</t>
+          <t>113752</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>288104</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>288104</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>288104</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>271226</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>271226</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>271226</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>252364</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>252364</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>252364</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>301018</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>301018</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>301018</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>677</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>572244</t>
+          <t>540468</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>572244</t>
+          <t>540468</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>572244</t>
+          <t>540468</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>77418</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>64065</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>93351</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>13,67%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>92862</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>75474</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>109000</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>87059</t>
+          <t>92948</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>71916</t>
+          <t>79007</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>105058</t>
+          <t>109340</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>179921</t>
+          <t>170365</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>156966</t>
+          <t>151963</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>203756</t>
+          <t>192118</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>148281</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>128968</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>170691</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>18,89%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>110744</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>90944</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>131473</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>162173</t>
+          <t>107532</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>140045</t>
+          <t>92789</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>186041</t>
+          <t>124292</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>272917</t>
+          <t>255813</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>241040</t>
+          <t>232392</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>301823</t>
+          <t>281777</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -4126,67 +4126,67 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>154617</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>135943</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>174878</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>139758</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>117069</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>162562</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>21,5%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>25,01%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>167350</t>
+          <t>137396</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>146559</t>
+          <t>119573</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>188540</t>
+          <t>156565</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>307108</t>
+          <t>292014</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>272879</t>
+          <t>264564</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>336200</t>
+          <t>317460</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>118808</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>101422</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>138677</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>119203</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>100901</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>141985</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>125468</t>
+          <t>114291</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>107541</t>
+          <t>98119</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>145141</t>
+          <t>130048</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>244671</t>
+          <t>233099</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>216611</t>
+          <t>208855</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>271559</t>
+          <t>260088</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>88589</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>71123</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>108099</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>108924</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>79793</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>192722</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>16,76%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>29,65%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>94359</t>
+          <t>85677</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>76601</t>
+          <t>72650</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>116508</t>
+          <t>102630</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>203283</t>
+          <t>174266</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>172030</t>
+          <t>151396</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>280696</t>
+          <t>196601</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>94993</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>76356</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>123374</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>78600</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>64296</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>96381</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>77390</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>63483</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>144583</t>
+          <t>93265</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>182943</t>
+          <t>172384</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>154387</t>
+          <t>149731</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>217996</t>
+          <t>203185</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>650092</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>650092</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>650092</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>615235</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>615235</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>615235</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>740752</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>740752</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>740752</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1850</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1390844</t>
+          <t>1297941</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1390844</t>
+          <t>1297941</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1390844</t>
+          <t>1297941</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
